--- a/ASIGNACION_C1_EQUIPO27.xlsx
+++ b/ASIGNACION_C1_EQUIPO27.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EQUIPO 27 - PARTICIPANTES" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MENSAJES BIENVENIDA" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESUMEN CC" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⚠️ REVISAR TELS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -68,7 +69,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -105,6 +106,11 @@
         <fgColor rgb="00D0E4F7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE5E5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -132,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -186,6 +192,10 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -558,14 +568,14 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="5" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="28" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
@@ -608,7 +618,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Teléfono</t>
+          <t>Teléfono (51+9)</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -628,7 +638,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Tel. IMO</t>
+          <t>Tel. IMO (51+9)</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -643,7 +653,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Tel. CC</t>
+          <t>Tel. CC (+51)</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -20205,10 +20215,10 @@
   <dimension ref="A1:F277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="80" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
@@ -20216,7 +20226,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>MENSAJES DE BIENVENIDA — 275 PX EQUIPO 27  (Solo Participantes, no IMOs)</t>
+          <t>MENSAJES DE BIENVENIDA — 275 PX EQUIPO 27  (Solo Participantes)</t>
         </is>
       </c>
     </row>
@@ -20238,7 +20248,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Tel. CC</t>
+          <t>Tel. CC (+51)</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -20275,13 +20285,14 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>Hola Clara! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Clara! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20315,13 +20326,14 @@
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>Hola Isabel! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Isabel! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20355,13 +20367,14 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Hola Fernando! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Fernando! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20395,13 +20408,14 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Hola Virginia! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Virginia! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20435,13 +20449,14 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Hola Nataly! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Nataly! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20475,13 +20490,14 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Hola Karina! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Karina! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20515,13 +20531,14 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Hola Jean! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jean! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20555,13 +20572,14 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Hola Jaime! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jaime! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20595,13 +20613,14 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Hola Juan! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Juan! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20635,13 +20654,14 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Hola Eddy! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Eddy! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20675,13 +20695,14 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Hola Pilar! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Pilar! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20715,13 +20736,14 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Hola Dorila! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Dorila! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20755,13 +20777,14 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Hola Beder! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Beder! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20795,13 +20818,14 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Hola Luz! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Luz! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20835,13 +20859,14 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Hola Milagros! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Milagros! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20875,13 +20900,14 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Hola Sebastian! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Sebastian! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20915,13 +20941,14 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Hola Maria! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20955,13 +20982,14 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Hola German! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola German! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20995,13 +21023,14 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Hola Felix! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Felix! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21035,13 +21064,14 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Hola Karina! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Karina! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21075,13 +21105,14 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Hola Eduardo! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Eduardo! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21115,13 +21146,14 @@
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Hola Milagros! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Milagros! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21155,13 +21187,14 @@
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Hola Adolfo! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Adolfo! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21195,13 +21228,14 @@
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Hola Francis! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Francis! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21235,13 +21269,14 @@
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Hola Greace! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Greace! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21275,13 +21310,14 @@
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>Hola Maribel! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Maribel! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21315,13 +21351,14 @@
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Hola Herminia! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Herminia! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21355,13 +21392,14 @@
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Hola Kevin! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Kevin! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21395,13 +21433,14 @@
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Hola Sumiko! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Sumiko! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21435,13 +21474,14 @@
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>Hola Carlos! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Carlos! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21475,13 +21515,14 @@
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Hola Christhian! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Christhian! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21515,13 +21556,14 @@
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>Hola Johann! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Johann! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21555,13 +21597,14 @@
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Hola Damaris! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Damaris! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21595,13 +21638,14 @@
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>Hola Patricia! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Patricia! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21635,13 +21679,14 @@
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Hola George! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola George! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21675,13 +21720,14 @@
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>Hola Jose! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jose! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21715,13 +21761,14 @@
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Hola Benjamin! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Benjamin! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21755,13 +21802,14 @@
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>Hola Pilar! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Pilar! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21795,13 +21843,14 @@
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Hola Isabel! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Isabel! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21835,13 +21884,14 @@
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>Hola Rosa! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Rosa! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21875,13 +21925,14 @@
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Hola Maria! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21915,13 +21966,14 @@
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>Hola Orlando! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Orlando! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21955,13 +22007,14 @@
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Hola Ana! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Ana! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21995,13 +22048,14 @@
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>Hola Melanie! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Melanie! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22035,13 +22089,14 @@
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Hola Joaquin! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Joaquin! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22075,13 +22130,14 @@
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>Hola Elida! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Elida! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22115,13 +22171,14 @@
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Hola David! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola David! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22155,13 +22212,14 @@
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>Hola Veronica! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Veronica! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22195,13 +22253,14 @@
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Hola Karilse! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Karilse! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22235,13 +22294,14 @@
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>Hola Ingri! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Ingri! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22275,13 +22335,14 @@
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Hola Sandra! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Sandra! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22315,13 +22376,14 @@
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>Hola Christian! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Christian! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22355,13 +22417,14 @@
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Hola Maria! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22395,13 +22458,14 @@
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>Hola Esperanza.! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Esperanza.! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22435,13 +22499,14 @@
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Hola Ana! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Ana! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22475,13 +22540,14 @@
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>Hola Sonia! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Sonia! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22515,13 +22581,14 @@
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Hola Gabriela! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Gabriela! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22555,13 +22622,14 @@
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>Hola Flor! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Flor! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22595,13 +22663,14 @@
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Hola Nicolas! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Nicolas! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22635,13 +22704,14 @@
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>Hola Alejandra! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Alejandra! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22675,13 +22745,14 @@
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Hola Sergio! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Sergio! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22715,13 +22786,14 @@
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>Hola Karina! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Karina! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22755,13 +22827,14 @@
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Hola Leonardo! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Leonardo! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22795,13 +22868,14 @@
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>Hola Katherine! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Katherine! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22835,13 +22909,14 @@
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Hola Yesenia! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Yesenia! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22875,13 +22950,14 @@
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>Hola Fredy! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Fredy! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22915,13 +22991,14 @@
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Hola Victor! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Victor! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22955,13 +23032,14 @@
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>Hola Karina! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Karina! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22995,13 +23073,14 @@
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Hola Elvira! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Elvira! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23035,13 +23114,14 @@
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>Hola Victor! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Victor! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23075,13 +23155,14 @@
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Hola Liliana! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Liliana! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23115,13 +23196,14 @@
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>Hola Luz! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Luz! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23155,13 +23237,14 @@
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Hola Jackelin! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jackelin! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23195,13 +23278,14 @@
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>Hola Esther! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Esther! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23235,13 +23319,14 @@
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Hola Natalia! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Natalia! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23275,13 +23360,14 @@
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>Hola Alexandra! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Alexandra! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23315,13 +23401,14 @@
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Hola Flor! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Flor! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23355,13 +23442,14 @@
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>Hola Zoilo! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Zoilo! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23395,13 +23483,14 @@
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Hola Rosario! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Rosario! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23435,13 +23524,14 @@
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>Hola Kelly! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Kelly! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23475,13 +23565,14 @@
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Hola Katherine! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Katherine! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23515,13 +23606,14 @@
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>Hola Noelia! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Noelia! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23555,13 +23647,14 @@
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Hola Ray! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Ray! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23595,13 +23688,14 @@
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>Hola Melvina! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Melvina! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23635,13 +23729,14 @@
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Hola Wilson! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Wilson! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23675,13 +23770,14 @@
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>Hola Jhon! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jhon! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23715,13 +23811,14 @@
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Hola Clarisa! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Clarisa! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23755,13 +23852,14 @@
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>Hola Silvana! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Silvana! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23795,13 +23893,14 @@
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Hola Rusel! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Rusel! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23835,13 +23934,14 @@
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>Hola Ruben! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Ruben! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23875,13 +23975,14 @@
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Hola Pedro! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Pedro! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23915,13 +24016,14 @@
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>Hola Rivaldo! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Rivaldo! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23955,13 +24057,14 @@
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Hola Sheylly! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Sheylly! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23995,13 +24098,14 @@
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>Hola Willy! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Willy! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24035,13 +24139,14 @@
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>Hola Herbert! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Herbert! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24075,13 +24180,14 @@
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>Hola Maria! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24115,13 +24221,14 @@
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>Hola Santos! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Santos! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24155,13 +24262,14 @@
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>Hola David! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola David! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24195,13 +24303,14 @@
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>Hola Elena! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Elena! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24235,13 +24344,14 @@
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>Hola Sebastian! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Sebastian! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su contacto: *+51 933 599 864*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 864*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24275,13 +24385,14 @@
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>Hola Melly! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Melly! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24315,13 +24426,14 @@
       </c>
       <c r="E104" s="13" t="inlineStr">
         <is>
-          <t>Hola Odette! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Odette! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24355,13 +24467,14 @@
       </c>
       <c r="E105" s="13" t="inlineStr">
         <is>
-          <t>Hola Sulmy! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Sulmy! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24395,13 +24508,14 @@
       </c>
       <c r="E106" s="13" t="inlineStr">
         <is>
-          <t>Hola Geraldine! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Geraldine! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24435,13 +24549,14 @@
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>Hola Maria! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24475,13 +24590,14 @@
       </c>
       <c r="E108" s="13" t="inlineStr">
         <is>
-          <t>Hola Angelo! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Angelo! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24515,13 +24631,14 @@
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>Hola Jose! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jose! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24555,13 +24672,14 @@
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>Hola Edwin! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Edwin! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24595,13 +24713,14 @@
       </c>
       <c r="E111" s="13" t="inlineStr">
         <is>
-          <t>Hola Billy! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Billy! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24635,13 +24754,14 @@
       </c>
       <c r="E112" s="13" t="inlineStr">
         <is>
-          <t>Hola Denise! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Denise! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24675,13 +24795,14 @@
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
-          <t>Hola Maria! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24715,13 +24836,14 @@
       </c>
       <c r="E114" s="13" t="inlineStr">
         <is>
-          <t>Hola Jose! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jose! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24755,13 +24877,14 @@
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>Hola Luis! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Luis! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24795,13 +24918,14 @@
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
-          <t>Hola Elvia! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Elvia! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24835,13 +24959,14 @@
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>Hola Pamela! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Pamela! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24875,13 +25000,14 @@
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>Hola Leonardo! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Leonardo! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24915,13 +25041,14 @@
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>Hola Fanny! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Fanny! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24955,13 +25082,14 @@
       </c>
       <c r="E120" s="13" t="inlineStr">
         <is>
-          <t>Hola Adriana! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Adriana! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24995,13 +25123,14 @@
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>Hola Teresa! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Teresa! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25035,13 +25164,14 @@
       </c>
       <c r="E122" s="13" t="inlineStr">
         <is>
-          <t>Hola Jhylda! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jhylda! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25075,13 +25205,14 @@
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>Hola Angela! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Angela! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25115,13 +25246,14 @@
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>Hola Kely! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Kely! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25155,13 +25287,14 @@
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>Hola Claudio! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Claudio! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25195,13 +25328,14 @@
       </c>
       <c r="E126" s="13" t="inlineStr">
         <is>
-          <t>Hola Asunta! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Asunta! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25235,13 +25369,14 @@
       </c>
       <c r="E127" s="13" t="inlineStr">
         <is>
-          <t>Hola Carmen! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Carmen! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25275,13 +25410,14 @@
       </c>
       <c r="E128" s="13" t="inlineStr">
         <is>
-          <t>Hola Giovanna! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Giovanna! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25315,13 +25451,14 @@
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>Hola Ana! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Ana! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25355,13 +25492,14 @@
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>Hola Camila! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Camila! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25395,13 +25533,14 @@
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>Hola Yamilet! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Yamilet! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25435,13 +25574,14 @@
       </c>
       <c r="E132" s="13" t="inlineStr">
         <is>
-          <t>Hola Clever! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Clever! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25475,13 +25615,14 @@
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>Hola Rosario! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Rosario! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25515,13 +25656,14 @@
       </c>
       <c r="E134" s="13" t="inlineStr">
         <is>
-          <t>Hola Wilber! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Wilber! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25555,13 +25697,14 @@
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>Hola Jose! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jose! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25595,13 +25738,14 @@
       </c>
       <c r="E136" s="13" t="inlineStr">
         <is>
-          <t>Hola Yadira! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Yadira! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25635,13 +25779,14 @@
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>Hola Douglas! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Douglas! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25675,13 +25820,14 @@
       </c>
       <c r="E138" s="13" t="inlineStr">
         <is>
-          <t>Hola Edgar! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Edgar! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25715,13 +25861,14 @@
       </c>
       <c r="E139" s="13" t="inlineStr">
         <is>
-          <t>Hola Heraclio! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Heraclio! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25755,13 +25902,14 @@
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>Hola Maria! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25795,13 +25943,14 @@
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>Hola Richard! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Richard! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25835,13 +25984,14 @@
       </c>
       <c r="E142" s="13" t="inlineStr">
         <is>
-          <t>Hola Mary! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Mary! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25875,13 +26025,14 @@
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>Hola Deizy! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Deizy! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25915,13 +26066,14 @@
       </c>
       <c r="E144" s="13" t="inlineStr">
         <is>
-          <t>Hola Fiorela! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Fiorela! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25955,13 +26107,14 @@
       </c>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>Hola Nicohol! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Nicohol! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25995,13 +26148,14 @@
       </c>
       <c r="E146" s="13" t="inlineStr">
         <is>
-          <t>Hola Sergio! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Sergio! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26035,13 +26189,14 @@
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>Hola Wilson! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Wilson! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26075,13 +26230,14 @@
       </c>
       <c r="E148" s="13" t="inlineStr">
         <is>
-          <t>Hola Maria! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26115,13 +26271,14 @@
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
-          <t>Hola Ruth! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Ruth! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26155,13 +26312,14 @@
       </c>
       <c r="E150" s="13" t="inlineStr">
         <is>
-          <t>Hola Jose! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jose! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26195,13 +26353,14 @@
       </c>
       <c r="E151" s="13" t="inlineStr">
         <is>
-          <t>Hola Mario! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Mario! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26235,13 +26394,14 @@
       </c>
       <c r="E152" s="13" t="inlineStr">
         <is>
-          <t>Hola Pedro! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Pedro! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26275,13 +26435,14 @@
       </c>
       <c r="E153" s="13" t="inlineStr">
         <is>
-          <t>Hola Daniela! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Daniela! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26315,13 +26476,14 @@
       </c>
       <c r="E154" s="13" t="inlineStr">
         <is>
-          <t>Hola Yby! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Yby! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26355,13 +26517,14 @@
       </c>
       <c r="E155" s="13" t="inlineStr">
         <is>
-          <t>Hola Deisse! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Deisse! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26395,13 +26558,14 @@
       </c>
       <c r="E156" s="13" t="inlineStr">
         <is>
-          <t>Hola Francisco! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Francisco! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26435,13 +26599,14 @@
       </c>
       <c r="E157" s="13" t="inlineStr">
         <is>
-          <t>Hola Giovana! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Giovana! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26475,13 +26640,14 @@
       </c>
       <c r="E158" s="13" t="inlineStr">
         <is>
-          <t>Hola Jackeline! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jackeline! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26515,13 +26681,14 @@
       </c>
       <c r="E159" s="13" t="inlineStr">
         <is>
-          <t>Hola Sheila! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Sheila! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26555,13 +26722,14 @@
       </c>
       <c r="E160" s="13" t="inlineStr">
         <is>
-          <t>Hola Juana! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Juana! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26595,13 +26763,14 @@
       </c>
       <c r="E161" s="13" t="inlineStr">
         <is>
-          <t>Hola Deivy! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Deivy! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26635,13 +26804,14 @@
       </c>
       <c r="E162" s="13" t="inlineStr">
         <is>
-          <t>Hola Christian! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Christian! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26675,13 +26845,14 @@
       </c>
       <c r="E163" s="13" t="inlineStr">
         <is>
-          <t>Hola Jorge! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jorge! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26715,13 +26886,14 @@
       </c>
       <c r="E164" s="13" t="inlineStr">
         <is>
-          <t>Hola Meliza! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Meliza! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26755,13 +26927,14 @@
       </c>
       <c r="E165" s="13" t="inlineStr">
         <is>
-          <t>Hola Maria! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26795,13 +26968,14 @@
       </c>
       <c r="E166" s="13" t="inlineStr">
         <is>
-          <t>Hola Flavio! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Flavio! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26835,13 +27009,14 @@
       </c>
       <c r="E167" s="13" t="inlineStr">
         <is>
-          <t>Hola Kevin! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Kevin! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26875,13 +27050,14 @@
       </c>
       <c r="E168" s="13" t="inlineStr">
         <is>
-          <t>Hola Hugo! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Hugo! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26915,13 +27091,14 @@
       </c>
       <c r="E169" s="13" t="inlineStr">
         <is>
-          <t>Hola Sergio! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Sergio! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26955,13 +27132,14 @@
       </c>
       <c r="E170" s="13" t="inlineStr">
         <is>
-          <t>Hola Jeferson! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jeferson! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26995,13 +27173,14 @@
       </c>
       <c r="E171" s="13" t="inlineStr">
         <is>
-          <t>Hola Andrea! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Andrea! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27035,13 +27214,14 @@
       </c>
       <c r="E172" s="13" t="inlineStr">
         <is>
-          <t>Hola Carmen! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Carmen! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27075,13 +27255,14 @@
       </c>
       <c r="E173" s="13" t="inlineStr">
         <is>
-          <t>Hola Margarita! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Margarita! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27115,13 +27296,14 @@
       </c>
       <c r="E174" s="13" t="inlineStr">
         <is>
-          <t>Hola Jesusa! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jesusa! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27155,13 +27337,14 @@
       </c>
       <c r="E175" s="13" t="inlineStr">
         <is>
-          <t>Hola Ralph! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Ralph! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27195,13 +27378,14 @@
       </c>
       <c r="E176" s="13" t="inlineStr">
         <is>
-          <t>Hola Sixto! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Sixto! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27235,13 +27419,14 @@
       </c>
       <c r="E177" s="13" t="inlineStr">
         <is>
-          <t>Hola Jose! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jose! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27275,13 +27460,14 @@
       </c>
       <c r="E178" s="13" t="inlineStr">
         <is>
-          <t>Hola Henry! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Henry! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27315,13 +27501,14 @@
       </c>
       <c r="E179" s="13" t="inlineStr">
         <is>
-          <t>Hola Luz! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Luz! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27355,13 +27542,14 @@
       </c>
       <c r="E180" s="13" t="inlineStr">
         <is>
-          <t>Hola Pepe! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Pepe! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27395,13 +27583,14 @@
       </c>
       <c r="E181" s="13" t="inlineStr">
         <is>
-          <t>Hola Flor! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Flor! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27435,13 +27624,14 @@
       </c>
       <c r="E182" s="13" t="inlineStr">
         <is>
-          <t>Hola Maruja! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Maruja! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27475,13 +27665,14 @@
       </c>
       <c r="E183" s="13" t="inlineStr">
         <is>
-          <t>Hola Jorge! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jorge! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27515,13 +27706,14 @@
       </c>
       <c r="E184" s="13" t="inlineStr">
         <is>
-          <t>Hola Marciano! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Marciano! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27555,13 +27747,14 @@
       </c>
       <c r="E185" s="13" t="inlineStr">
         <is>
-          <t>Hola Anali! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Anali! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27595,13 +27788,14 @@
       </c>
       <c r="E186" s="13" t="inlineStr">
         <is>
-          <t>Hola Gabriela! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Gabriela! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27635,13 +27829,14 @@
       </c>
       <c r="E187" s="13" t="inlineStr">
         <is>
-          <t>Hola Rebeca! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Rebeca! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27675,13 +27870,14 @@
       </c>
       <c r="E188" s="13" t="inlineStr">
         <is>
-          <t>Hola Joel! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Joel! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27715,13 +27911,14 @@
       </c>
       <c r="E189" s="13" t="inlineStr">
         <is>
-          <t>Hola Natividad! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Natividad! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27755,13 +27952,14 @@
       </c>
       <c r="E190" s="13" t="inlineStr">
         <is>
-          <t>Hola Rebecca! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Rebecca! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27795,13 +27993,14 @@
       </c>
       <c r="E191" s="13" t="inlineStr">
         <is>
-          <t>Hola Lesly! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Lesly! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27835,13 +28034,14 @@
       </c>
       <c r="E192" s="13" t="inlineStr">
         <is>
-          <t>Hola Claudio! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Claudio! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27875,13 +28075,14 @@
       </c>
       <c r="E193" s="13" t="inlineStr">
         <is>
-          <t>Hola Jessica! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jessica! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27915,13 +28116,14 @@
       </c>
       <c r="E194" s="13" t="inlineStr">
         <is>
-          <t>Hola Javier! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Javier! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27955,13 +28157,14 @@
       </c>
       <c r="E195" s="13" t="inlineStr">
         <is>
-          <t>Hola Clelia! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Clelia! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su contacto: *+51 912 379 744*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 912 379 744*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27995,13 +28198,14 @@
       </c>
       <c r="E196" s="9" t="inlineStr">
         <is>
-          <t>Hola Bania! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Bania! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28035,13 +28239,14 @@
       </c>
       <c r="E197" s="9" t="inlineStr">
         <is>
-          <t>Hola Mabel! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Mabel! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28075,13 +28280,14 @@
       </c>
       <c r="E198" s="9" t="inlineStr">
         <is>
-          <t>Hola Maria! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28115,13 +28321,14 @@
       </c>
       <c r="E199" s="9" t="inlineStr">
         <is>
-          <t>Hola Nestor! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Nestor! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28155,13 +28362,14 @@
       </c>
       <c r="E200" s="9" t="inlineStr">
         <is>
-          <t>Hola Maria! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28195,13 +28403,14 @@
       </c>
       <c r="E201" s="9" t="inlineStr">
         <is>
-          <t>Hola Rosario! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Rosario! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28235,13 +28444,14 @@
       </c>
       <c r="E202" s="9" t="inlineStr">
         <is>
-          <t>Hola Nicolas! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Nicolas! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28275,13 +28485,14 @@
       </c>
       <c r="E203" s="9" t="inlineStr">
         <is>
-          <t>Hola Maria! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28315,13 +28526,14 @@
       </c>
       <c r="E204" s="9" t="inlineStr">
         <is>
-          <t>Hola Edgar! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Edgar! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28355,13 +28567,14 @@
       </c>
       <c r="E205" s="9" t="inlineStr">
         <is>
-          <t>Hola Magaly! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Magaly! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28395,13 +28608,14 @@
       </c>
       <c r="E206" s="9" t="inlineStr">
         <is>
-          <t>Hola Victor! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Victor! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28435,13 +28649,14 @@
       </c>
       <c r="E207" s="9" t="inlineStr">
         <is>
-          <t>Hola Rocio! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Rocio! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28475,13 +28690,14 @@
       </c>
       <c r="E208" s="9" t="inlineStr">
         <is>
-          <t>Hola Luzmila! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Luzmila! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28515,13 +28731,14 @@
       </c>
       <c r="E209" s="9" t="inlineStr">
         <is>
-          <t>Hola Diego! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Diego! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28555,13 +28772,14 @@
       </c>
       <c r="E210" s="9" t="inlineStr">
         <is>
-          <t>Hola Miriam! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Miriam! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28595,13 +28813,14 @@
       </c>
       <c r="E211" s="9" t="inlineStr">
         <is>
-          <t>Hola Jose! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jose! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28635,13 +28854,14 @@
       </c>
       <c r="E212" s="9" t="inlineStr">
         <is>
-          <t>Hola Avelina! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Avelina! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28675,13 +28895,14 @@
       </c>
       <c r="E213" s="9" t="inlineStr">
         <is>
-          <t>Hola Hugo! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Hugo! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28715,13 +28936,14 @@
       </c>
       <c r="E214" s="9" t="inlineStr">
         <is>
-          <t>Hola Juan! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Juan! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28755,13 +28977,14 @@
       </c>
       <c r="E215" s="9" t="inlineStr">
         <is>
-          <t>Hola Milton! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Milton! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28795,13 +29018,14 @@
       </c>
       <c r="E216" s="9" t="inlineStr">
         <is>
-          <t>Hola Angelica! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Angelica! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28835,13 +29059,14 @@
       </c>
       <c r="E217" s="9" t="inlineStr">
         <is>
-          <t>Hola Helman! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Helman! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28875,13 +29100,14 @@
       </c>
       <c r="E218" s="9" t="inlineStr">
         <is>
-          <t>Hola Yudith! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Yudith! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28915,13 +29141,14 @@
       </c>
       <c r="E219" s="9" t="inlineStr">
         <is>
-          <t>Hola Tania! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Tania! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28955,13 +29182,14 @@
       </c>
       <c r="E220" s="9" t="inlineStr">
         <is>
-          <t>Hola Roger! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Roger! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28995,13 +29223,14 @@
       </c>
       <c r="E221" s="9" t="inlineStr">
         <is>
-          <t>Hola Velinda! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Velinda! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29035,13 +29264,14 @@
       </c>
       <c r="E222" s="9" t="inlineStr">
         <is>
-          <t>Hola Jonatan! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jonatan! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29075,13 +29305,14 @@
       </c>
       <c r="E223" s="9" t="inlineStr">
         <is>
-          <t>Hola Odalis! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Odalis! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29115,13 +29346,14 @@
       </c>
       <c r="E224" s="9" t="inlineStr">
         <is>
-          <t>Hola Santos! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Santos! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29155,13 +29387,14 @@
       </c>
       <c r="E225" s="9" t="inlineStr">
         <is>
-          <t>Hola Mayra! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Mayra! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29195,13 +29428,14 @@
       </c>
       <c r="E226" s="9" t="inlineStr">
         <is>
-          <t>Hola Basilia! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Basilia! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29235,13 +29469,14 @@
       </c>
       <c r="E227" s="9" t="inlineStr">
         <is>
-          <t>Hola Edgard! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Edgard! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29275,13 +29510,14 @@
       </c>
       <c r="E228" s="9" t="inlineStr">
         <is>
-          <t>Hola Jose! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jose! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29315,13 +29551,14 @@
       </c>
       <c r="E229" s="9" t="inlineStr">
         <is>
-          <t>Hola Sebastian! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Sebastian! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29355,13 +29592,14 @@
       </c>
       <c r="E230" s="9" t="inlineStr">
         <is>
-          <t>Hola Tati! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Tati! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29395,13 +29633,14 @@
       </c>
       <c r="E231" s="9" t="inlineStr">
         <is>
-          <t>Hola Jhosef! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jhosef! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29435,13 +29674,14 @@
       </c>
       <c r="E232" s="9" t="inlineStr">
         <is>
-          <t>Hola Wilma! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Wilma! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29475,13 +29715,14 @@
       </c>
       <c r="E233" s="9" t="inlineStr">
         <is>
-          <t>Hola Felipe! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Felipe! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29515,13 +29756,14 @@
       </c>
       <c r="E234" s="9" t="inlineStr">
         <is>
-          <t>Hola Jhonny! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jhonny! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29555,13 +29797,14 @@
       </c>
       <c r="E235" s="9" t="inlineStr">
         <is>
-          <t>Hola Camila! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Camila! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29595,13 +29838,14 @@
       </c>
       <c r="E236" s="9" t="inlineStr">
         <is>
-          <t>Hola Miguel! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Miguel! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29635,13 +29879,14 @@
       </c>
       <c r="E237" s="9" t="inlineStr">
         <is>
-          <t>Hola Esther! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Esther! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29675,13 +29920,14 @@
       </c>
       <c r="E238" s="9" t="inlineStr">
         <is>
-          <t>Hola Luis! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Luis! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29715,13 +29961,14 @@
       </c>
       <c r="E239" s="9" t="inlineStr">
         <is>
-          <t>Hola Grisselly! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Grisselly! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29755,13 +30002,14 @@
       </c>
       <c r="E240" s="9" t="inlineStr">
         <is>
-          <t>Hola Kevin! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Kevin! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29795,13 +30043,14 @@
       </c>
       <c r="E241" s="9" t="inlineStr">
         <is>
-          <t>Hola Joaquin! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Joaquin! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29835,13 +30084,14 @@
       </c>
       <c r="E242" s="9" t="inlineStr">
         <is>
-          <t>Hola Lucila! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Lucila! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29875,13 +30125,14 @@
       </c>
       <c r="E243" s="9" t="inlineStr">
         <is>
-          <t>Hola Celestina! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Celestina! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29915,13 +30166,14 @@
       </c>
       <c r="E244" s="9" t="inlineStr">
         <is>
-          <t>Hola Luis! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Luis! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29955,13 +30207,14 @@
       </c>
       <c r="E245" s="9" t="inlineStr">
         <is>
-          <t>Hola Jocser! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jocser! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29995,13 +30248,14 @@
       </c>
       <c r="E246" s="9" t="inlineStr">
         <is>
-          <t>Hola Mario! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Mario! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30035,13 +30289,14 @@
       </c>
       <c r="E247" s="9" t="inlineStr">
         <is>
-          <t>Hola Rosa! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Rosa! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30075,13 +30330,14 @@
       </c>
       <c r="E248" s="9" t="inlineStr">
         <is>
-          <t>Hola Reveli! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Reveli! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30115,13 +30371,14 @@
       </c>
       <c r="E249" s="9" t="inlineStr">
         <is>
-          <t>Hola Maritza! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Maritza! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30155,13 +30412,14 @@
       </c>
       <c r="E250" s="9" t="inlineStr">
         <is>
-          <t>Hola Marcos! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Marcos! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30195,13 +30453,14 @@
       </c>
       <c r="E251" s="9" t="inlineStr">
         <is>
-          <t>Hola Silvia! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Silvia! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30235,13 +30494,14 @@
       </c>
       <c r="E252" s="9" t="inlineStr">
         <is>
-          <t>Hola Prisila! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Prisila! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30275,13 +30535,14 @@
       </c>
       <c r="E253" s="9" t="inlineStr">
         <is>
-          <t>Hola Fiorela! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Fiorela! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30315,13 +30576,14 @@
       </c>
       <c r="E254" s="9" t="inlineStr">
         <is>
-          <t>Hola Filomena! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Filomena! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30355,13 +30617,14 @@
       </c>
       <c r="E255" s="9" t="inlineStr">
         <is>
-          <t>Hola Ingrid! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Ingrid! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30395,13 +30658,14 @@
       </c>
       <c r="E256" s="9" t="inlineStr">
         <is>
-          <t>Hola Sandy! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Sandy! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30435,13 +30699,14 @@
       </c>
       <c r="E257" s="9" t="inlineStr">
         <is>
-          <t>Hola Edwin! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Edwin! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30475,13 +30740,14 @@
       </c>
       <c r="E258" s="9" t="inlineStr">
         <is>
-          <t>Hola Juan! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Juan! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30515,13 +30781,14 @@
       </c>
       <c r="E259" s="9" t="inlineStr">
         <is>
-          <t>Hola Rosina! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Rosina! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30555,13 +30822,14 @@
       </c>
       <c r="E260" s="9" t="inlineStr">
         <is>
-          <t>Hola Yamilet! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Yamilet! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30595,13 +30863,14 @@
       </c>
       <c r="E261" s="9" t="inlineStr">
         <is>
-          <t>Hola Mardonia! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Mardonia! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30635,13 +30904,14 @@
       </c>
       <c r="E262" s="9" t="inlineStr">
         <is>
-          <t>Hola Dora! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Dora! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30675,13 +30945,14 @@
       </c>
       <c r="E263" s="9" t="inlineStr">
         <is>
-          <t>Hola Matthew! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Matthew! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30715,13 +30986,14 @@
       </c>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>Hola Luis! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Luis! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30755,13 +31027,14 @@
       </c>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>Hola Carol! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Carol! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30795,13 +31068,14 @@
       </c>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>Hola Xiomara! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Xiomara! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30835,13 +31109,14 @@
       </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>Hola Flor! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Flor! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30875,13 +31150,14 @@
       </c>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>Hola Katherin! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Katherin! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30915,13 +31191,14 @@
       </c>
       <c r="E269" s="9" t="inlineStr">
         <is>
-          <t>Hola Jhon! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jhon! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30955,13 +31232,14 @@
       </c>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>Hola Jhon! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jhon! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30995,13 +31273,14 @@
       </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>Hola Marlene! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Marlene! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31035,13 +31314,14 @@
       </c>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>Hola Mirza! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Mirza! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31075,13 +31355,14 @@
       </c>
       <c r="E273" s="9" t="inlineStr">
         <is>
-          <t>Hola Lizbeth! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Lizbeth! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31115,13 +31396,14 @@
       </c>
       <c r="E274" s="9" t="inlineStr">
         <is>
-          <t>Hola Jhofree! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Jhofree! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31155,13 +31437,14 @@
       </c>
       <c r="E275" s="9" t="inlineStr">
         <is>
-          <t>Hola Gabriel! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Gabriel! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31195,13 +31478,14 @@
       </c>
       <c r="E276" s="9" t="inlineStr">
         <is>
-          <t>Hola Yesenia! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Yesenia! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31235,13 +31519,14 @@
       </c>
       <c r="E277" s="9" t="inlineStr">
         <is>
-          <t>Hola Frank! Bienvenido/a a *Crear Poder Sin Límites Perú* — Equipo 27.
-Tienes un cupo reservado para *C1 E27*:
+          <t>Hola Frank! Te escribimos desde *Crear Poder Sin Límites Perú*.
+Bienvenido/a al *Equipo 27* — C1 E27.
+📅 *Fechas:*
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
 Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su contacto: *+51 933 599 903*
-Ella te acompañará en todo el proceso.
+Te pedimos guardar su número: *+51 933 599 903*
+Ella te contactará para acompañarte en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31266,13 +31551,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -31290,7 +31576,7 @@
       </c>
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>Teléfono</t>
+          <t>Teléfono (+51)</t>
         </is>
       </c>
       <c r="C2" s="15" t="inlineStr">
@@ -31301,6 +31587,11 @@
       <c r="D2" s="15" t="inlineStr">
         <is>
           <t>% Equipo</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>Color en archivo</t>
         </is>
       </c>
     </row>
@@ -31323,6 +31614,11 @@
           <t>33.5%</t>
         </is>
       </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>Azul claro</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
@@ -31343,6 +31639,11 @@
           <t>33.1%</t>
         </is>
       </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>Verde claro</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
@@ -31361,6 +31662,11 @@
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t>33.5%</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>Morado claro</t>
         </is>
       </c>
     </row>
@@ -31379,11 +31685,116 @@
           <t>100%</t>
         </is>
       </c>
+      <c r="E6" s="22" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C112"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Nombre Completo</t>
+        </is>
+      </c>
+      <c r="B1" s="23" t="inlineStr">
+        <is>
+          <t>Tel Original (problema)</t>
+        </is>
+      </c>
+      <c r="C1" s="23" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Nieto Nolasco Billy Roussbelt</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>9921081654</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>Diana Moscoso</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Valentin Sanchez Nicohol Loyzitt</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>92216433004</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>Diana Moscoso</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="24" t="inlineStr">
+        <is>
+          <t>Salvatierra Nolazco Jose Eduardo</t>
+        </is>
+      </c>
+      <c r="B102" s="24" t="inlineStr">
+        <is>
+          <t>9974099987</t>
+        </is>
+      </c>
+      <c r="C102" s="24" t="inlineStr">
+        <is>
+          <t>Joyce Marín</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="24" t="inlineStr">
+        <is>
+          <t>Torres Angulo Velinda Clayredt</t>
+        </is>
+      </c>
+      <c r="B112" s="24" t="inlineStr">
+        <is>
+          <t>9601116315</t>
+        </is>
+      </c>
+      <c r="C112" s="24" t="inlineStr">
+        <is>
+          <t>Joyce Marín</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/ASIGNACION_C1_EQUIPO27.xlsx
+++ b/ASIGNACION_C1_EQUIPO27.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EQUIPO 27 - PARTICIPANTES" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EQUIPO 27 - C1 E27" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MENSAJES BIENVENIDA" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESUMEN CC" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⚠️ REVISAR TELS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVISAR TELS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -584,14 +584,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>EQUIPO 27 — C1 E27  |  275 Participantes  |  CPSL Lima</t>
+          <t>EQUIPO 27 — C1 E27  |  275 Creadores Cuánticos  |  CPSL Lima</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Joyce: 91  |  Zuley: 92  |  Diana: 92  |  01–03 Mayo 2026  |  Hotel José Antonio Deluxe, Miraflores</t>
+          <t>Enrolados FDS 17–19 Abr 2026  |  Joyce: 91  |  Zuley: 92  |  Diana: 92  |  01–03 Mayo 2026  |  Hotel José Antonio Deluxe</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Teléfono (51+9)</t>
+          <t>Teléfono</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Tel. IMO (51+9)</t>
+          <t>Tel. IMO</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -20226,24 +20226,24 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>MENSAJES DE BIENVENIDA — 275 PX EQUIPO 27  (Solo Participantes)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
+          <t>MENSAJES BIENVENIDA — 275 Creadores Cuánticos E27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Teléfono PX</t>
+          <t>Teléfono</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Nombre PX</t>
+          <t>Nombre Completo</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>CC Asignada</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Estado Envío</t>
+          <t>Estado</t>
         </is>
       </c>
     </row>
@@ -20287,12 +20287,12 @@
         <is>
           <t>Hola Clara! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20328,12 +20328,12 @@
         <is>
           <t>Hola Isabel! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20369,12 +20369,12 @@
         <is>
           <t>Hola Fernando! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20410,12 +20410,12 @@
         <is>
           <t>Hola Virginia! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20451,12 +20451,12 @@
         <is>
           <t>Hola Nataly! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20492,12 +20492,12 @@
         <is>
           <t>Hola Karina! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20533,12 +20533,12 @@
         <is>
           <t>Hola Jean! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20574,12 +20574,12 @@
         <is>
           <t>Hola Jaime! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20615,12 +20615,12 @@
         <is>
           <t>Hola Juan! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20656,12 +20656,12 @@
         <is>
           <t>Hola Eddy! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20697,12 +20697,12 @@
         <is>
           <t>Hola Pilar! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20738,12 +20738,12 @@
         <is>
           <t>Hola Dorila! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20779,12 +20779,12 @@
         <is>
           <t>Hola Beder! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20820,12 +20820,12 @@
         <is>
           <t>Hola Luz! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20861,12 +20861,12 @@
         <is>
           <t>Hola Milagros! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20902,12 +20902,12 @@
         <is>
           <t>Hola Sebastian! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20943,12 +20943,12 @@
         <is>
           <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -20984,12 +20984,12 @@
         <is>
           <t>Hola German! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21025,12 +21025,12 @@
         <is>
           <t>Hola Felix! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21066,12 +21066,12 @@
         <is>
           <t>Hola Karina! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21107,12 +21107,12 @@
         <is>
           <t>Hola Eduardo! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21148,12 +21148,12 @@
         <is>
           <t>Hola Milagros! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21189,12 +21189,12 @@
         <is>
           <t>Hola Adolfo! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21230,12 +21230,12 @@
         <is>
           <t>Hola Francis! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21271,12 +21271,12 @@
         <is>
           <t>Hola Greace! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21312,12 +21312,12 @@
         <is>
           <t>Hola Maribel! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21353,12 +21353,12 @@
         <is>
           <t>Hola Herminia! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21394,12 +21394,12 @@
         <is>
           <t>Hola Kevin! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21435,12 +21435,12 @@
         <is>
           <t>Hola Sumiko! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21476,12 +21476,12 @@
         <is>
           <t>Hola Carlos! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21517,12 +21517,12 @@
         <is>
           <t>Hola Christhian! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21558,12 +21558,12 @@
         <is>
           <t>Hola Johann! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21599,12 +21599,12 @@
         <is>
           <t>Hola Damaris! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21640,12 +21640,12 @@
         <is>
           <t>Hola Patricia! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21681,12 +21681,12 @@
         <is>
           <t>Hola George! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21722,12 +21722,12 @@
         <is>
           <t>Hola Jose! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21763,12 +21763,12 @@
         <is>
           <t>Hola Benjamin! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21804,12 +21804,12 @@
         <is>
           <t>Hola Pilar! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21845,12 +21845,12 @@
         <is>
           <t>Hola Isabel! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21886,12 +21886,12 @@
         <is>
           <t>Hola Rosa! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21927,12 +21927,12 @@
         <is>
           <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -21968,12 +21968,12 @@
         <is>
           <t>Hola Orlando! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22009,12 +22009,12 @@
         <is>
           <t>Hola Ana! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22050,12 +22050,12 @@
         <is>
           <t>Hola Melanie! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22091,12 +22091,12 @@
         <is>
           <t>Hola Joaquin! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22132,12 +22132,12 @@
         <is>
           <t>Hola Elida! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22173,12 +22173,12 @@
         <is>
           <t>Hola David! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22214,12 +22214,12 @@
         <is>
           <t>Hola Veronica! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22255,12 +22255,12 @@
         <is>
           <t>Hola Karilse! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22296,12 +22296,12 @@
         <is>
           <t>Hola Ingri! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22337,12 +22337,12 @@
         <is>
           <t>Hola Sandra! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22378,12 +22378,12 @@
         <is>
           <t>Hola Christian! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22419,12 +22419,12 @@
         <is>
           <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22460,12 +22460,12 @@
         <is>
           <t>Hola Esperanza.! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22501,12 +22501,12 @@
         <is>
           <t>Hola Ana! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22542,12 +22542,12 @@
         <is>
           <t>Hola Sonia! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22583,12 +22583,12 @@
         <is>
           <t>Hola Gabriela! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22624,12 +22624,12 @@
         <is>
           <t>Hola Flor! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22665,12 +22665,12 @@
         <is>
           <t>Hola Nicolas! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22706,12 +22706,12 @@
         <is>
           <t>Hola Alejandra! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22747,12 +22747,12 @@
         <is>
           <t>Hola Sergio! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22788,12 +22788,12 @@
         <is>
           <t>Hola Karina! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22829,12 +22829,12 @@
         <is>
           <t>Hola Leonardo! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22870,12 +22870,12 @@
         <is>
           <t>Hola Katherine! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22911,12 +22911,12 @@
         <is>
           <t>Hola Yesenia! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22952,12 +22952,12 @@
         <is>
           <t>Hola Fredy! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -22993,12 +22993,12 @@
         <is>
           <t>Hola Victor! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23034,12 +23034,12 @@
         <is>
           <t>Hola Karina! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23075,12 +23075,12 @@
         <is>
           <t>Hola Elvira! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23116,12 +23116,12 @@
         <is>
           <t>Hola Victor! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23157,12 +23157,12 @@
         <is>
           <t>Hola Liliana! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23198,12 +23198,12 @@
         <is>
           <t>Hola Luz! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23239,12 +23239,12 @@
         <is>
           <t>Hola Jackelin! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23280,12 +23280,12 @@
         <is>
           <t>Hola Esther! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23321,12 +23321,12 @@
         <is>
           <t>Hola Natalia! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23362,12 +23362,12 @@
         <is>
           <t>Hola Alexandra! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23403,12 +23403,12 @@
         <is>
           <t>Hola Flor! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23444,12 +23444,12 @@
         <is>
           <t>Hola Zoilo! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23485,12 +23485,12 @@
         <is>
           <t>Hola Rosario! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23526,12 +23526,12 @@
         <is>
           <t>Hola Kelly! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23567,12 +23567,12 @@
         <is>
           <t>Hola Katherine! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23608,12 +23608,12 @@
         <is>
           <t>Hola Noelia! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23649,12 +23649,12 @@
         <is>
           <t>Hola Ray! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23690,12 +23690,12 @@
         <is>
           <t>Hola Melvina! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23731,12 +23731,12 @@
         <is>
           <t>Hola Wilson! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23772,12 +23772,12 @@
         <is>
           <t>Hola Jhon! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23813,12 +23813,12 @@
         <is>
           <t>Hola Clarisa! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23854,12 +23854,12 @@
         <is>
           <t>Hola Silvana! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23895,12 +23895,12 @@
         <is>
           <t>Hola Rusel! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23936,12 +23936,12 @@
         <is>
           <t>Hola Ruben! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -23977,12 +23977,12 @@
         <is>
           <t>Hola Pedro! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24018,12 +24018,12 @@
         <is>
           <t>Hola Rivaldo! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24059,12 +24059,12 @@
         <is>
           <t>Hola Sheylly! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24100,12 +24100,12 @@
         <is>
           <t>Hola Willy! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24141,12 +24141,12 @@
         <is>
           <t>Hola Herbert! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24182,12 +24182,12 @@
         <is>
           <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24223,12 +24223,12 @@
         <is>
           <t>Hola Santos! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24264,12 +24264,12 @@
         <is>
           <t>Hola David! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24305,12 +24305,12 @@
         <is>
           <t>Hola Elena! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24346,12 +24346,12 @@
         <is>
           <t>Hola Sebastian! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Zuley Urteaga*.
-Te pedimos guardar su número: *+51 933 599 864*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Zuley Urteaga*.
+Guarda su número: *+51 933 599 864*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24387,12 +24387,12 @@
         <is>
           <t>Hola Melly! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24428,12 +24428,12 @@
         <is>
           <t>Hola Odette! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24469,12 +24469,12 @@
         <is>
           <t>Hola Sulmy! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24510,12 +24510,12 @@
         <is>
           <t>Hola Geraldine! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24551,12 +24551,12 @@
         <is>
           <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24592,12 +24592,12 @@
         <is>
           <t>Hola Angelo! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24633,12 +24633,12 @@
         <is>
           <t>Hola Jose! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24674,12 +24674,12 @@
         <is>
           <t>Hola Edwin! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24715,12 +24715,12 @@
         <is>
           <t>Hola Billy! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24756,12 +24756,12 @@
         <is>
           <t>Hola Denise! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24797,12 +24797,12 @@
         <is>
           <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24838,12 +24838,12 @@
         <is>
           <t>Hola Jose! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24879,12 +24879,12 @@
         <is>
           <t>Hola Luis! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24920,12 +24920,12 @@
         <is>
           <t>Hola Elvia! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -24961,12 +24961,12 @@
         <is>
           <t>Hola Pamela! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25002,12 +25002,12 @@
         <is>
           <t>Hola Leonardo! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25043,12 +25043,12 @@
         <is>
           <t>Hola Fanny! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25084,12 +25084,12 @@
         <is>
           <t>Hola Adriana! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25125,12 +25125,12 @@
         <is>
           <t>Hola Teresa! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25166,12 +25166,12 @@
         <is>
           <t>Hola Jhylda! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25207,12 +25207,12 @@
         <is>
           <t>Hola Angela! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25248,12 +25248,12 @@
         <is>
           <t>Hola Kely! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25289,12 +25289,12 @@
         <is>
           <t>Hola Claudio! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25330,12 +25330,12 @@
         <is>
           <t>Hola Asunta! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25371,12 +25371,12 @@
         <is>
           <t>Hola Carmen! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25412,12 +25412,12 @@
         <is>
           <t>Hola Giovanna! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25453,12 +25453,12 @@
         <is>
           <t>Hola Ana! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25494,12 +25494,12 @@
         <is>
           <t>Hola Camila! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25535,12 +25535,12 @@
         <is>
           <t>Hola Yamilet! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25576,12 +25576,12 @@
         <is>
           <t>Hola Clever! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25617,12 +25617,12 @@
         <is>
           <t>Hola Rosario! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25658,12 +25658,12 @@
         <is>
           <t>Hola Wilber! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25699,12 +25699,12 @@
         <is>
           <t>Hola Jose! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25740,12 +25740,12 @@
         <is>
           <t>Hola Yadira! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25781,12 +25781,12 @@
         <is>
           <t>Hola Douglas! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25822,12 +25822,12 @@
         <is>
           <t>Hola Edgar! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25863,12 +25863,12 @@
         <is>
           <t>Hola Heraclio! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25904,12 +25904,12 @@
         <is>
           <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25945,12 +25945,12 @@
         <is>
           <t>Hola Richard! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -25986,12 +25986,12 @@
         <is>
           <t>Hola Mary! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26027,12 +26027,12 @@
         <is>
           <t>Hola Deizy! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26068,12 +26068,12 @@
         <is>
           <t>Hola Fiorela! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26109,12 +26109,12 @@
         <is>
           <t>Hola Nicohol! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26150,12 +26150,12 @@
         <is>
           <t>Hola Sergio! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26191,12 +26191,12 @@
         <is>
           <t>Hola Wilson! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26232,12 +26232,12 @@
         <is>
           <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26273,12 +26273,12 @@
         <is>
           <t>Hola Ruth! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26314,12 +26314,12 @@
         <is>
           <t>Hola Jose! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26355,12 +26355,12 @@
         <is>
           <t>Hola Mario! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26396,12 +26396,12 @@
         <is>
           <t>Hola Pedro! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26437,12 +26437,12 @@
         <is>
           <t>Hola Daniela! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26478,12 +26478,12 @@
         <is>
           <t>Hola Yby! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26519,12 +26519,12 @@
         <is>
           <t>Hola Deisse! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26560,12 +26560,12 @@
         <is>
           <t>Hola Francisco! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26601,12 +26601,12 @@
         <is>
           <t>Hola Giovana! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26642,12 +26642,12 @@
         <is>
           <t>Hola Jackeline! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26683,12 +26683,12 @@
         <is>
           <t>Hola Sheila! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26724,12 +26724,12 @@
         <is>
           <t>Hola Juana! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26765,12 +26765,12 @@
         <is>
           <t>Hola Deivy! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26806,12 +26806,12 @@
         <is>
           <t>Hola Christian! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26847,12 +26847,12 @@
         <is>
           <t>Hola Jorge! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26888,12 +26888,12 @@
         <is>
           <t>Hola Meliza! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26929,12 +26929,12 @@
         <is>
           <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -26970,12 +26970,12 @@
         <is>
           <t>Hola Flavio! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27011,12 +27011,12 @@
         <is>
           <t>Hola Kevin! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27052,12 +27052,12 @@
         <is>
           <t>Hola Hugo! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27093,12 +27093,12 @@
         <is>
           <t>Hola Sergio! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27134,12 +27134,12 @@
         <is>
           <t>Hola Jeferson! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27175,12 +27175,12 @@
         <is>
           <t>Hola Andrea! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27216,12 +27216,12 @@
         <is>
           <t>Hola Carmen! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27257,12 +27257,12 @@
         <is>
           <t>Hola Margarita! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27298,12 +27298,12 @@
         <is>
           <t>Hola Jesusa! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27339,12 +27339,12 @@
         <is>
           <t>Hola Ralph! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27380,12 +27380,12 @@
         <is>
           <t>Hola Sixto! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27421,12 +27421,12 @@
         <is>
           <t>Hola Jose! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27462,12 +27462,12 @@
         <is>
           <t>Hola Henry! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27503,12 +27503,12 @@
         <is>
           <t>Hola Luz! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27544,12 +27544,12 @@
         <is>
           <t>Hola Pepe! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27585,12 +27585,12 @@
         <is>
           <t>Hola Flor! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27626,12 +27626,12 @@
         <is>
           <t>Hola Maruja! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27667,12 +27667,12 @@
         <is>
           <t>Hola Jorge! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27708,12 +27708,12 @@
         <is>
           <t>Hola Marciano! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27749,12 +27749,12 @@
         <is>
           <t>Hola Anali! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27790,12 +27790,12 @@
         <is>
           <t>Hola Gabriela! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27831,12 +27831,12 @@
         <is>
           <t>Hola Rebeca! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27872,12 +27872,12 @@
         <is>
           <t>Hola Joel! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27913,12 +27913,12 @@
         <is>
           <t>Hola Natividad! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27954,12 +27954,12 @@
         <is>
           <t>Hola Rebecca! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -27995,12 +27995,12 @@
         <is>
           <t>Hola Lesly! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28036,12 +28036,12 @@
         <is>
           <t>Hola Claudio! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28077,12 +28077,12 @@
         <is>
           <t>Hola Jessica! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28118,12 +28118,12 @@
         <is>
           <t>Hola Javier! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28159,12 +28159,12 @@
         <is>
           <t>Hola Clelia! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Diana Moscoso*.
-Te pedimos guardar su número: *+51 912 379 744*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Diana Moscoso*.
+Guarda su número: *+51 912 379 744*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28200,12 +28200,12 @@
         <is>
           <t>Hola Bania! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28241,12 +28241,12 @@
         <is>
           <t>Hola Mabel! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28282,12 +28282,12 @@
         <is>
           <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28323,12 +28323,12 @@
         <is>
           <t>Hola Nestor! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28364,12 +28364,12 @@
         <is>
           <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28405,12 +28405,12 @@
         <is>
           <t>Hola Rosario! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28446,12 +28446,12 @@
         <is>
           <t>Hola Nicolas! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28487,12 +28487,12 @@
         <is>
           <t>Hola Maria! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28528,12 +28528,12 @@
         <is>
           <t>Hola Edgar! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28569,12 +28569,12 @@
         <is>
           <t>Hola Magaly! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28610,12 +28610,12 @@
         <is>
           <t>Hola Victor! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28651,12 +28651,12 @@
         <is>
           <t>Hola Rocio! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28692,12 +28692,12 @@
         <is>
           <t>Hola Luzmila! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28733,12 +28733,12 @@
         <is>
           <t>Hola Diego! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28774,12 +28774,12 @@
         <is>
           <t>Hola Miriam! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28815,12 +28815,12 @@
         <is>
           <t>Hola Jose! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28856,12 +28856,12 @@
         <is>
           <t>Hola Avelina! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28897,12 +28897,12 @@
         <is>
           <t>Hola Hugo! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28938,12 +28938,12 @@
         <is>
           <t>Hola Juan! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -28979,12 +28979,12 @@
         <is>
           <t>Hola Milton! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29020,12 +29020,12 @@
         <is>
           <t>Hola Angelica! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29061,12 +29061,12 @@
         <is>
           <t>Hola Helman! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29102,12 +29102,12 @@
         <is>
           <t>Hola Yudith! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29143,12 +29143,12 @@
         <is>
           <t>Hola Tania! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29184,12 +29184,12 @@
         <is>
           <t>Hola Roger! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29225,12 +29225,12 @@
         <is>
           <t>Hola Velinda! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29266,12 +29266,12 @@
         <is>
           <t>Hola Jonatan! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29307,12 +29307,12 @@
         <is>
           <t>Hola Odalis! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29348,12 +29348,12 @@
         <is>
           <t>Hola Santos! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29389,12 +29389,12 @@
         <is>
           <t>Hola Mayra! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29430,12 +29430,12 @@
         <is>
           <t>Hola Basilia! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29471,12 +29471,12 @@
         <is>
           <t>Hola Edgard! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29512,12 +29512,12 @@
         <is>
           <t>Hola Jose! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29553,12 +29553,12 @@
         <is>
           <t>Hola Sebastian! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29594,12 +29594,12 @@
         <is>
           <t>Hola Tati! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29635,12 +29635,12 @@
         <is>
           <t>Hola Jhosef! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29676,12 +29676,12 @@
         <is>
           <t>Hola Wilma! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29717,12 +29717,12 @@
         <is>
           <t>Hola Felipe! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29758,12 +29758,12 @@
         <is>
           <t>Hola Jhonny! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29799,12 +29799,12 @@
         <is>
           <t>Hola Camila! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29840,12 +29840,12 @@
         <is>
           <t>Hola Miguel! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29881,12 +29881,12 @@
         <is>
           <t>Hola Esther! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29922,12 +29922,12 @@
         <is>
           <t>Hola Luis! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -29963,12 +29963,12 @@
         <is>
           <t>Hola Grisselly! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30004,12 +30004,12 @@
         <is>
           <t>Hola Kevin! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30045,12 +30045,12 @@
         <is>
           <t>Hola Joaquin! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30086,12 +30086,12 @@
         <is>
           <t>Hola Lucila! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30127,12 +30127,12 @@
         <is>
           <t>Hola Celestina! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30168,12 +30168,12 @@
         <is>
           <t>Hola Luis! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30209,12 +30209,12 @@
         <is>
           <t>Hola Jocser! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30250,12 +30250,12 @@
         <is>
           <t>Hola Mario! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30291,12 +30291,12 @@
         <is>
           <t>Hola Rosa! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30332,12 +30332,12 @@
         <is>
           <t>Hola Reveli! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30373,12 +30373,12 @@
         <is>
           <t>Hola Maritza! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30414,12 +30414,12 @@
         <is>
           <t>Hola Marcos! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30455,12 +30455,12 @@
         <is>
           <t>Hola Silvia! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30496,12 +30496,12 @@
         <is>
           <t>Hola Prisila! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30537,12 +30537,12 @@
         <is>
           <t>Hola Fiorela! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30578,12 +30578,12 @@
         <is>
           <t>Hola Filomena! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30619,12 +30619,12 @@
         <is>
           <t>Hola Ingrid! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30660,12 +30660,12 @@
         <is>
           <t>Hola Sandy! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30701,12 +30701,12 @@
         <is>
           <t>Hola Edwin! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30742,12 +30742,12 @@
         <is>
           <t>Hola Juan! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30783,12 +30783,12 @@
         <is>
           <t>Hola Rosina! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30824,12 +30824,12 @@
         <is>
           <t>Hola Yamilet! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30865,12 +30865,12 @@
         <is>
           <t>Hola Mardonia! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30906,12 +30906,12 @@
         <is>
           <t>Hola Dora! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30947,12 +30947,12 @@
         <is>
           <t>Hola Matthew! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -30988,12 +30988,12 @@
         <is>
           <t>Hola Luis! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31029,12 +31029,12 @@
         <is>
           <t>Hola Carol! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31070,12 +31070,12 @@
         <is>
           <t>Hola Xiomara! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31111,12 +31111,12 @@
         <is>
           <t>Hola Flor! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31152,12 +31152,12 @@
         <is>
           <t>Hola Katherin! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31193,12 +31193,12 @@
         <is>
           <t>Hola Jhon! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31234,12 +31234,12 @@
         <is>
           <t>Hola Jhon! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31275,12 +31275,12 @@
         <is>
           <t>Hola Marlene! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31316,12 +31316,12 @@
         <is>
           <t>Hola Mirza! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31357,12 +31357,12 @@
         <is>
           <t>Hola Lizbeth! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31398,12 +31398,12 @@
         <is>
           <t>Hola Jhofree! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31439,12 +31439,12 @@
         <is>
           <t>Hola Gabriel! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31480,12 +31480,12 @@
         <is>
           <t>Hola Yesenia! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31521,12 +31521,12 @@
         <is>
           <t>Hola Frank! Te escribimos desde *Crear Poder Sin Límites Perú*.
 Bienvenido/a al *Equipo 27* — C1 E27.
-📅 *Fechas:*
+Tu lugar en el entrenamiento ya está confirmado:
 Viernes 01, Sábado 02 y Domingo 03 de Mayo 2026
-📍 Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
-Tu coordinadora asignada es *Joyce Marín*.
-Te pedimos guardar su número: *+51 933 599 903*
-Ella te contactará para acompañarte en el proceso.
+Hotel José Antonio Deluxe, Calle Bellavista 133, Miraflores.
+Tu coordinadora es *Joyce Marín*.
+Guarda su número: *+51 933 599 903*
+Ella te acompañará en el proceso.
 Nos vemos en la cancha. ⚡
 *CPSL Lima*</t>
         </is>
@@ -31556,9 +31556,9 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -31581,7 +31581,7 @@
       </c>
       <c r="C2" s="15" t="inlineStr">
         <is>
-          <t>Total PX</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D2" s="15" t="inlineStr">
@@ -31591,7 +31591,7 @@
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
-          <t>Color en archivo</t>
+          <t>Color</t>
         </is>
       </c>
     </row>
@@ -31616,7 +31616,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>Azul claro</t>
+          <t>Azul</t>
         </is>
       </c>
     </row>
@@ -31641,7 +31641,7 @@
       </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
-          <t>Verde claro</t>
+          <t>Verde</t>
         </is>
       </c>
     </row>
@@ -31666,7 +31666,7 @@
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>Morado claro</t>
+          <t>Morado</t>
         </is>
       </c>
     </row>
@@ -31717,7 +31717,7 @@
       </c>
       <c r="B1" s="23" t="inlineStr">
         <is>
-          <t>Tel Original (problema)</t>
+          <t>Teléfono (revisar)</t>
         </is>
       </c>
       <c r="C1" s="23" t="inlineStr">
